--- a/docs/files/exports/combined-combined-requirements-complete-guide.xlsx
+++ b/docs/files/exports/combined-combined-requirements-complete-guide.xlsx
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Combined Web + App Requirements Complete Guide</t>
+          <t>Requirements Complete Guide</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -451,12 +451,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11,384 words</t>
+          <t>11,383 words</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Combined Web + App Requirements Complete Guide Comprehensive requirements guide covering both website/web application and mobile application projects in a single reference document. Scope: This document covers both Web /...</t>
+          <t>Requirements Complete Guide Master reference guide documenting all technical requirement categories for both Website and Mobile Application projects — ideal for comprehensive scoping, proposal writing, and technical spec...</t>
         </is>
       </c>
     </row>
